--- a/docs/golden-set/guard-blind/2026-10-14-guard-128-blind.xlsx
+++ b/docs/golden-set/guard-blind/2026-10-14-guard-128-blind.xlsx
@@ -8503,7 +8503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -8540,7 +8540,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>只能依本列的證據判斷，不可查網路或用自己的知識。</t>
+          <t>只能依本列的證據判斷，不可查網路找答案、也不可用自己的知識補足；但可以用翻譯工具讀懂英文證據。</t>
         </is>
       </c>
     </row>
@@ -8548,6 +8548,20 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>請勿查看其他工作表或對照答案檔；標完後交回。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>由 2 位標註者各自獨立標註（標完前不互相討論、不交換檔案），用來計算兩人一致性 Cohen's κ（目標 ≥ 0.7）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>請勿使用本系統或請 LLM 代為判斷。可分次標註；標完存檔交回，檔名請加上你的名字縮寫。</t>
         </is>
       </c>
     </row>
